--- a/template/t6_ocr_report.xlsx
+++ b/template/t6_ocr_report.xlsx
@@ -58,7 +58,7 @@
     <t>micro_0074_YSA.jpg</t>
   </si>
   <si>
-    <t>micro_0100_XIV.jpg</t>
+    <t>micro_0055_XIV.jpg</t>
   </si>
   <si>
     <t>micro_0000_XZI.jpg</t>
@@ -67,13 +67,13 @@
     <t>micro_0045_XZT.jpg</t>
   </si>
   <si>
-    <t>micro_0103_XN_K1224.jpg</t>
+    <t>micro_0102_XN_K1224.jpg</t>
   </si>
   <si>
     <t>micro_0027_XL_II.jpg</t>
   </si>
   <si>
-    <t>micro_0093_XL_I_HO_00.jpg</t>
+    <t>micro_0092_XL_I_HO_00.jpg</t>
   </si>
   <si>
     <t>micro_0005_X8.jpg</t>
@@ -91,13 +91,13 @@
     <t>micro_0035_X_O_2460_0O0.jpg</t>
   </si>
   <si>
-    <t>micro_0018_HSIV.jpg</t>
+    <t>micro_0085_HSIV.jpg</t>
   </si>
   <si>
     <t>micro_0019_HSII.jpg</t>
   </si>
   <si>
-    <t>micro_0085__5c0f_D.jpg</t>
+    <t>micro_0050_SI.jpg</t>
   </si>
   <si>
     <t>micro_0064_DOQOOSN.jpg</t>
@@ -130,13 +130,13 @@
     <t>micro_0063_D6.jpg</t>
   </si>
   <si>
-    <t>micro_0092_D58.jpg</t>
+    <t>micro_0091_D58.jpg</t>
   </si>
   <si>
     <t>micro_0060_D56.jpg</t>
   </si>
   <si>
-    <t>micro_0095_D52.jpg</t>
+    <t>micro_0094_D52.jpg</t>
   </si>
   <si>
     <t>micro_0003_D50.jpg</t>
@@ -199,13 +199,13 @@
     <t>micro_0011_D18.jpg</t>
   </si>
   <si>
-    <t>micro_0087_D17.jpg</t>
+    <t>micro_0086_D17.jpg</t>
   </si>
   <si>
     <t>micro_0077_0D16.jpg</t>
   </si>
   <si>
-    <t>micro_0088_D15.jpg</t>
+    <t>micro_0087_D15.jpg</t>
   </si>
   <si>
     <t>micro_0052_D14.jpg</t>
@@ -819,7 +819,7 @@
         <v>70</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.9954721331596375</v>
       </c>
       <c r="D3" t="s">
         <v>125</v>
@@ -901,7 +901,7 @@
         <v>72</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.994575023651123</v>
       </c>
       <c r="D5" t="s">
         <v>125</v>
@@ -942,7 +942,7 @@
         <v>73</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.9976063966751099</v>
       </c>
       <c r="D6" t="s">
         <v>125</v>
@@ -983,7 +983,7 @@
         <v>74</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.9574066996574402</v>
       </c>
       <c r="D7" t="s">
         <v>125</v>
@@ -1065,7 +1065,7 @@
         <v>76</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.9929895401000977</v>
       </c>
       <c r="D9" t="s">
         <v>125</v>
@@ -1074,13 +1074,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>1049</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>21.09814963797265</v>
+        <v>0</v>
       </c>
       <c r="I9" t="s">
         <v>126</v>
@@ -1106,7 +1106,7 @@
         <v>77</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.9879199266433716</v>
       </c>
       <c r="D10" t="s">
         <v>125</v>
@@ -1115,13 +1115,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>933</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>20.66445182724252</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>126</v>
@@ -1147,7 +1147,7 @@
         <v>78</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0.9893468022346497</v>
       </c>
       <c r="D11" t="s">
         <v>125</v>
@@ -1156,13 +1156,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>1106</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>18.39654025282768</v>
+        <v>0</v>
       </c>
       <c r="I11" t="s">
         <v>126</v>
@@ -1188,7 +1188,7 @@
         <v>79</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0.9856538772583008</v>
       </c>
       <c r="D12" t="s">
         <v>125</v>
@@ -1197,13 +1197,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>1077</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>20.11580127007845</v>
+        <v>0</v>
       </c>
       <c r="I12" t="s">
         <v>126</v>
@@ -1229,7 +1229,7 @@
         <v>80</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0.9884187579154968</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -1270,7 +1270,7 @@
         <v>81</v>
       </c>
       <c r="C14">
-        <v>0.9987279772758484</v>
+        <v>0.9985411763191223</v>
       </c>
       <c r="D14" t="s">
         <v>125</v>
@@ -1352,7 +1352,7 @@
         <v>83</v>
       </c>
       <c r="C16">
-        <v>0.7686963677406311</v>
+        <v>0.7308483719825745</v>
       </c>
       <c r="D16" t="s">
         <v>125</v>
@@ -1361,13 +1361,13 @@
         <v>1</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>16.87826736370426</v>
+        <v>0</v>
       </c>
       <c r="I16" t="s">
         <v>126</v>
@@ -1484,13 +1484,13 @@
         <v>1</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>1073</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>18.56080262930289</v>
+        <v>0</v>
       </c>
       <c r="I19" t="s">
         <v>126</v>
@@ -1525,13 +1525,13 @@
         <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>1089</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>18.06569343065694</v>
+        <v>0</v>
       </c>
       <c r="I20" t="s">
         <v>126</v>
@@ -1566,13 +1566,13 @@
         <v>1</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>17.74868157846881</v>
+        <v>0</v>
       </c>
       <c r="I21" t="s">
         <v>126</v>
@@ -1607,13 +1607,13 @@
         <v>1</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>979</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>18.43344003012615</v>
+        <v>0</v>
       </c>
       <c r="I22" t="s">
         <v>126</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:13">

--- a/template/t6_ocr_report.xlsx
+++ b/template/t6_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="128">
   <si>
     <t>filename</t>
   </si>
@@ -55,6 +55,9 @@
     <t>blue_centers</t>
   </si>
   <si>
+    <t>white_centers</t>
+  </si>
+  <si>
     <t>micro_0074_YSA.jpg</t>
   </si>
   <si>
@@ -103,7 +106,7 @@
     <t>micro_0064_DOQOOSN.jpg</t>
   </si>
   <si>
-    <t>micro_0065_ISA.jpg</t>
+    <t>micro_0021_SA.jpg</t>
   </si>
   <si>
     <t>micro_0082_S8.jpg</t>
@@ -726,10 +729,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -769,19 +772,22 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2">
-        <v>0.9988348484039307</v>
+        <v>0.9990420341491699</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -796,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -810,19 +816,22 @@
       <c r="M2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3">
         <v>0.9954721331596375</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -837,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -851,19 +860,22 @@
       <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4">
-        <v>0.9653985500335693</v>
+        <v>0.9048922061920166</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -878,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -892,19 +904,22 @@
       <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5">
         <v>0.994575023651123</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -919,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -933,19 +948,22 @@
       <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6">
-        <v>0.9976063966751099</v>
+        <v>0.9972390532493591</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -960,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -974,19 +992,22 @@
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7">
         <v>0.9574066996574402</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1001,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1015,19 +1036,22 @@
       <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8">
-        <v>0.968250036239624</v>
+        <v>0.9225170612335205</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1042,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1056,19 +1080,22 @@
       <c r="M8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>0.9929895401000977</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1083,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1097,19 +1124,22 @@
       <c r="M9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10">
         <v>0.9879199266433716</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1124,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1138,19 +1168,22 @@
       <c r="M10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11">
         <v>0.9893468022346497</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1165,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1179,19 +1212,22 @@
       <c r="M11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12">
         <v>0.9856538772583008</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1206,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1220,19 +1256,22 @@
       <c r="M12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13">
-        <v>0.9884187579154968</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1247,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1261,19 +1300,22 @@
       <c r="M13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14">
-        <v>0.9985411763191223</v>
+        <v>0.99773770570755</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1288,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1302,19 +1344,22 @@
       <c r="M14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15">
-        <v>0.7864853739738464</v>
+        <v>0.8552407622337341</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1329,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1343,19 +1388,22 @@
       <c r="M15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16">
-        <v>0.7308483719825745</v>
+        <v>0.738556444644928</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1370,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1384,19 +1432,22 @@
       <c r="M16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17">
-        <v>0.9966676235198975</v>
+        <v>0.997689425945282</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1411,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1425,19 +1476,22 @@
       <c r="M17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18">
-        <v>0.9957866072654724</v>
+        <v>0.9971151351928711</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1452,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1466,19 +1520,22 @@
       <c r="M18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C19">
-        <v>0.9913022518157959</v>
+        <v>0.9920763969421387</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1493,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1507,19 +1564,22 @@
       <c r="M19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20">
-        <v>0.9942432641983032</v>
+        <v>0.9916169047355652</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1534,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1548,19 +1608,22 @@
       <c r="M20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21">
-        <v>0.9960646629333496</v>
+        <v>0.9961717128753662</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1575,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1589,19 +1652,22 @@
       <c r="M21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22">
-        <v>0.9983569979667664</v>
+        <v>0.9980621933937073</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1616,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1630,19 +1696,22 @@
       <c r="M22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23">
-        <v>0.5664469599723816</v>
+        <v>0.9753515720367432</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1657,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1671,19 +1740,22 @@
       <c r="M23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0.9979174137115479</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1698,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1712,19 +1784,22 @@
       <c r="M24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0.99732905626297</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1739,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1753,19 +1828,22 @@
       <c r="M25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0.9974136352539062</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1780,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1794,19 +1872,22 @@
       <c r="M26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0.9995241165161133</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1821,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1835,19 +1916,22 @@
       <c r="M27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0.9993172287940979</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1862,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1876,19 +1960,22 @@
       <c r="M28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0.9956278800964355</v>
       </c>
       <c r="D29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1903,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1917,19 +2004,22 @@
       <c r="M29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0.9771170020103455</v>
       </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1944,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1958,19 +2048,22 @@
       <c r="M30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0.9971212148666382</v>
       </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1985,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1999,19 +2092,22 @@
       <c r="M31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0.9815649390220642</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2026,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -2040,19 +2136,22 @@
       <c r="M32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0.9995045065879822</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2067,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -2076,967 +2175,1039 @@
         <v>2</v>
       </c>
       <c r="L33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0.9996736645698547</v>
       </c>
       <c r="D34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
+        <v>127</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35">
+        <v>0.9621144533157349</v>
+      </c>
+      <c r="D35" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
+        <v>127</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36">
+        <v>0.9994654655456543</v>
+      </c>
+      <c r="D36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="s">
+        <v>127</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37">
+        <v>0.9921097755432129</v>
+      </c>
+      <c r="D37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" t="s">
+        <v>127</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38">
+        <v>0.9924885630607605</v>
+      </c>
+      <c r="D38" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>127</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39">
+        <v>0.9947871565818787</v>
+      </c>
+      <c r="D39" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="s">
+        <v>127</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40">
+        <v>0.9985910058021545</v>
+      </c>
+      <c r="D40" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40" t="s">
+        <v>127</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41">
+        <v>0.9894359707832336</v>
+      </c>
+      <c r="D41" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41" t="s">
+        <v>127</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>1</v>
+      </c>
+      <c r="N41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42">
+        <v>0.9997044205665588</v>
+      </c>
+      <c r="D42" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42" t="s">
+        <v>127</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43">
+        <v>0.9993259310722351</v>
+      </c>
+      <c r="D43" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="s">
+        <v>127</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44">
+        <v>0.9975537657737732</v>
+      </c>
+      <c r="D44" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44" t="s">
+        <v>127</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45">
+        <v>0.999352753162384</v>
+      </c>
+      <c r="D45" t="s">
+        <v>126</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45" t="s">
+        <v>127</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46">
+        <v>0.9978439807891846</v>
+      </c>
+      <c r="D46" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>127</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47">
+        <v>0.9600651860237122</v>
+      </c>
+      <c r="D47" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>127</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>126</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>127</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49">
+        <v>0.9984846115112305</v>
+      </c>
+      <c r="D49" t="s">
+        <v>126</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49" t="s">
+        <v>127</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50">
+        <v>0.9990313649177551</v>
+      </c>
+      <c r="D50" t="s">
+        <v>126</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50" t="s">
+        <v>127</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>63</v>
+      </c>
+      <c r="B51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51">
+        <v>0.9985432624816895</v>
+      </c>
+      <c r="D51" t="s">
+        <v>126</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51" t="s">
+        <v>127</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>64</v>
+      </c>
+      <c r="B52" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52">
+        <v>0.9841215014457703</v>
+      </c>
+      <c r="D52" t="s">
+        <v>126</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
+        <v>127</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>65</v>
+      </c>
+      <c r="B53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53">
+        <v>0.9983500838279724</v>
+      </c>
+      <c r="D53" t="s">
+        <v>126</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" t="s">
+        <v>127</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>1</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54">
+        <v>0.9809226989746094</v>
+      </c>
+      <c r="D54" t="s">
+        <v>126</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54" t="s">
+        <v>127</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55">
+        <v>0.9973804354667664</v>
+      </c>
+      <c r="D55" t="s">
+        <v>126</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="s">
+        <v>127</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>68</v>
+      </c>
+      <c r="B56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56">
+        <v>0.9980894923210144</v>
+      </c>
+      <c r="D56" t="s">
+        <v>126</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>127</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
         <v>125</v>
       </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34" t="s">
-        <v>126</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35" t="s">
-        <v>126</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36" t="s">
-        <v>125</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36" t="s">
-        <v>126</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37" t="s">
-        <v>125</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37" t="s">
-        <v>126</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38" t="s">
-        <v>126</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39" t="s">
-        <v>126</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40" t="s">
-        <v>126</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" t="s">
-        <v>52</v>
-      </c>
-      <c r="B41" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41" t="s">
-        <v>125</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41" t="s">
-        <v>126</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42" t="s">
-        <v>125</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42" t="s">
-        <v>126</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="A43" t="s">
-        <v>54</v>
-      </c>
-      <c r="B43" t="s">
-        <v>110</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43" t="s">
-        <v>126</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" t="s">
-        <v>111</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44" t="s">
-        <v>126</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45" t="s">
-        <v>126</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" t="s">
-        <v>113</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46" t="s">
-        <v>126</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" t="s">
-        <v>114</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47" t="s">
-        <v>126</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" t="s">
-        <v>115</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48" t="s">
-        <v>126</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="A49" t="s">
-        <v>60</v>
-      </c>
-      <c r="B49" t="s">
-        <v>116</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49" t="s">
-        <v>125</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49" t="s">
-        <v>126</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" t="s">
-        <v>61</v>
-      </c>
-      <c r="B50" t="s">
-        <v>117</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50" t="s">
-        <v>126</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
-      <c r="A51" t="s">
-        <v>62</v>
-      </c>
-      <c r="B51" t="s">
-        <v>118</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51" t="s">
-        <v>126</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
-      <c r="A52" t="s">
-        <v>63</v>
-      </c>
-      <c r="B52" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" t="s">
-        <v>125</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52" t="s">
-        <v>126</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
-      <c r="A53" t="s">
-        <v>64</v>
-      </c>
-      <c r="B53" t="s">
-        <v>120</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" t="s">
-        <v>125</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53" t="b">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53" t="s">
-        <v>126</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
-      <c r="A54" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" t="s">
-        <v>121</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54" t="s">
-        <v>126</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="A55" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" t="s">
-        <v>122</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>125</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55" t="s">
-        <v>126</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="A56" t="s">
-        <v>67</v>
-      </c>
-      <c r="B56" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" t="s">
-        <v>125</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56" t="s">
-        <v>126</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
-      <c r="A57" t="s">
-        <v>68</v>
-      </c>
-      <c r="B57" t="s">
-        <v>124</v>
-      </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3051,18 +3222,21 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57">
+        <v>1</v>
+      </c>
+      <c r="N57">
         <v>1</v>
       </c>
     </row>

--- a/template/t6_ocr_report.xlsx
+++ b/template/t6_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="130">
   <si>
     <t>filename</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>white_centers</t>
+  </si>
+  <si>
+    <t>is_tri</t>
+  </si>
+  <si>
+    <t>is_double</t>
   </si>
   <si>
     <t>micro_0074_YSA.jpg</t>
@@ -729,10 +735,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -775,19 +781,25 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>0.9990420341491699</v>
+        <v>0.9988731741905212</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -802,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -819,19 +831,25 @@
       <c r="N2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>0.9954721331596375</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -846,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -863,19 +881,25 @@
       <c r="N3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>0.9048922061920166</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -890,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -907,19 +931,25 @@
       <c r="N4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5">
-        <v>0.994575023651123</v>
+        <v>0.8647018074989319</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -934,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -951,19 +981,25 @@
       <c r="N5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6">
         <v>0.9972390532493591</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -978,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -995,19 +1031,25 @@
       <c r="N6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7">
         <v>0.9574066996574402</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1022,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1039,19 +1081,25 @@
       <c r="N7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8">
         <v>0.9225170612335205</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1066,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1083,19 +1131,25 @@
       <c r="N8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9">
         <v>0.9929895401000977</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1110,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1127,19 +1181,25 @@
       <c r="N9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>0.9879199266433716</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1154,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1171,19 +1231,25 @@
       <c r="N10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C11">
         <v>0.9893468022346497</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1198,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1215,19 +1281,25 @@
       <c r="N11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C12">
         <v>0.9856538772583008</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1242,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1259,19 +1331,25 @@
       <c r="N12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1286,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1303,19 +1381,25 @@
       <c r="N13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C14">
         <v>0.99773770570755</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1330,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1347,19 +1431,25 @@
       <c r="N14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C15">
         <v>0.8552407622337341</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1374,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1391,19 +1481,25 @@
       <c r="N15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C16">
         <v>0.738556444644928</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1418,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1435,19 +1531,25 @@
       <c r="N16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C17">
         <v>0.997689425945282</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1462,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1479,19 +1581,25 @@
       <c r="N17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C18">
         <v>0.9971151351928711</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1506,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1523,19 +1631,25 @@
       <c r="N18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C19">
         <v>0.9920763969421387</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1550,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1567,19 +1681,25 @@
       <c r="N19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C20">
         <v>0.9916169047355652</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1594,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1611,19 +1731,25 @@
       <c r="N20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C21">
         <v>0.9961717128753662</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1638,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1655,19 +1781,25 @@
       <c r="N21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C22">
         <v>0.9980621933937073</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1682,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1699,19 +1831,25 @@
       <c r="N22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C23">
         <v>0.9753515720367432</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1726,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1743,19 +1881,25 @@
       <c r="N23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24">
-        <v>0.9979174137115479</v>
+        <v>0.9977332353591919</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1770,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1785,21 +1929,27 @@
         <v>1</v>
       </c>
       <c r="N24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C25">
-        <v>0.99732905626297</v>
+        <v>0.9971137046813965</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1814,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1829,21 +1979,27 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C26">
-        <v>0.9974136352539062</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1858,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1875,19 +2031,25 @@
       <c r="N26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C27">
-        <v>0.9995241165161133</v>
+        <v>0.9995245933532715</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1902,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1917,21 +2079,27 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C28">
-        <v>0.9993172287940979</v>
+        <v>0.9993060231208801</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1946,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1963,19 +2131,25 @@
       <c r="N28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C29">
-        <v>0.9956278800964355</v>
+        <v>0.9944143295288086</v>
       </c>
       <c r="D29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1990,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2007,19 +2181,25 @@
       <c r="N29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C30">
-        <v>0.9771170020103455</v>
+        <v>0.9767656326293945</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2034,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2049,21 +2229,27 @@
         <v>1</v>
       </c>
       <c r="N30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C31">
-        <v>0.9971212148666382</v>
+        <v>0.9972039461135864</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2078,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -2093,21 +2279,27 @@
         <v>1</v>
       </c>
       <c r="N31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C32">
-        <v>0.9815649390220642</v>
+        <v>0.9783324599266052</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2122,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -2139,19 +2331,25 @@
       <c r="N32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C33">
         <v>0.9995045065879822</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2166,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -2183,1031 +2381,1175 @@
       <c r="N33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C34">
-        <v>0.9996736645698547</v>
+        <v>0.999666690826416</v>
       </c>
       <c r="D34" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
+        <v>129</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35">
+        <v>0.956432580947876</v>
+      </c>
+      <c r="D35" t="s">
+        <v>128</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
+        <v>129</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36">
+        <v>0.9994809031486511</v>
+      </c>
+      <c r="D36" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="s">
+        <v>129</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37">
+        <v>0.9912053942680359</v>
+      </c>
+      <c r="D37" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" t="s">
+        <v>129</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38">
+        <v>0.9925408363342285</v>
+      </c>
+      <c r="D38" t="s">
+        <v>128</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>129</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39">
+        <v>0.9964321255683899</v>
+      </c>
+      <c r="D39" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="s">
+        <v>129</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40">
+        <v>0.9987018704414368</v>
+      </c>
+      <c r="D40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40" t="s">
+        <v>129</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41">
+        <v>0.9894289374351501</v>
+      </c>
+      <c r="D41" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41" t="s">
+        <v>129</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>1</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42">
+        <v>0.9997012615203857</v>
+      </c>
+      <c r="D42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42" t="s">
+        <v>129</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43">
+        <v>0.9992678165435791</v>
+      </c>
+      <c r="D43" t="s">
+        <v>128</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="s">
+        <v>129</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44">
+        <v>0.9977620244026184</v>
+      </c>
+      <c r="D44" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44" t="s">
+        <v>129</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45">
+        <v>0.9992626309394836</v>
+      </c>
+      <c r="D45" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45" t="s">
+        <v>129</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46">
+        <v>0.9980854988098145</v>
+      </c>
+      <c r="D46" t="s">
+        <v>128</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>129</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47">
+        <v>0.9642094969749451</v>
+      </c>
+      <c r="D47" t="s">
+        <v>128</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>129</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>129</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49">
+        <v>0.9984526634216309</v>
+      </c>
+      <c r="D49" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49" t="s">
+        <v>129</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50">
+        <v>0.9990410208702087</v>
+      </c>
+      <c r="D50" t="s">
+        <v>128</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50" t="s">
+        <v>129</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51">
+        <v>0.9987942576408386</v>
+      </c>
+      <c r="D51" t="s">
+        <v>128</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51" t="s">
+        <v>129</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52">
+        <v>0.9838816523551941</v>
+      </c>
+      <c r="D52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
+        <v>129</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53">
+        <v>0.9983298182487488</v>
+      </c>
+      <c r="D53" t="s">
+        <v>128</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" t="s">
+        <v>129</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>1</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54">
+        <v>0.9798585176467896</v>
+      </c>
+      <c r="D54" t="s">
+        <v>128</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54" t="s">
+        <v>129</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55">
+        <v>0.9977080225944519</v>
+      </c>
+      <c r="D55" t="s">
+        <v>128</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="s">
+        <v>129</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" t="s">
         <v>126</v>
       </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="C56">
+        <v>0.9980642795562744</v>
+      </c>
+      <c r="D56" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>129</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" t="s">
         <v>127</v>
       </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35">
-        <v>0.9621144533157349</v>
-      </c>
-      <c r="D35" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35" t="s">
-        <v>127</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-      <c r="N35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36">
-        <v>0.9994654655456543</v>
-      </c>
-      <c r="D36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36" t="s">
-        <v>127</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="N36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37">
-        <v>0.9921097755432129</v>
-      </c>
-      <c r="D37" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37" t="s">
-        <v>127</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
-      <c r="N37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38">
-        <v>0.9924885630607605</v>
-      </c>
-      <c r="D38" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38" t="s">
-        <v>127</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>1</v>
-      </c>
-      <c r="N38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39">
-        <v>0.9947871565818787</v>
-      </c>
-      <c r="D39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39" t="s">
-        <v>127</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>1</v>
-      </c>
-      <c r="N39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40">
-        <v>0.9985910058021545</v>
-      </c>
-      <c r="D40" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40" t="s">
-        <v>127</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="N40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" t="s">
-        <v>53</v>
-      </c>
-      <c r="B41" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41">
-        <v>0.9894359707832336</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41" t="s">
-        <v>127</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>1</v>
-      </c>
-      <c r="N41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42">
-        <v>0.9997044205665588</v>
-      </c>
-      <c r="D42" t="s">
-        <v>126</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42" t="s">
-        <v>127</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
-      <c r="N42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" t="s">
-        <v>55</v>
-      </c>
-      <c r="B43" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43">
-        <v>0.9993259310722351</v>
-      </c>
-      <c r="D43" t="s">
-        <v>126</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43" t="s">
-        <v>127</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>1</v>
-      </c>
-      <c r="N43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B44" t="s">
-        <v>112</v>
-      </c>
-      <c r="C44">
-        <v>0.9975537657737732</v>
-      </c>
-      <c r="D44" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44" t="s">
-        <v>127</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
-      <c r="N44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" t="s">
-        <v>113</v>
-      </c>
-      <c r="C45">
-        <v>0.999352753162384</v>
-      </c>
-      <c r="D45" t="s">
-        <v>126</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45" t="s">
-        <v>127</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>1</v>
-      </c>
-      <c r="N45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C46">
-        <v>0.9978439807891846</v>
-      </c>
-      <c r="D46" t="s">
-        <v>126</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46" t="s">
-        <v>127</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-      <c r="N46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47" t="s">
-        <v>115</v>
-      </c>
-      <c r="C47">
-        <v>0.9600651860237122</v>
-      </c>
-      <c r="D47" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47" t="s">
-        <v>127</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>1</v>
-      </c>
-      <c r="N47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="A48" t="s">
-        <v>60</v>
-      </c>
-      <c r="B48" t="s">
-        <v>116</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48" t="s">
-        <v>127</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>1</v>
-      </c>
-      <c r="N48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" t="s">
-        <v>117</v>
-      </c>
-      <c r="C49">
-        <v>0.9984846115112305</v>
-      </c>
-      <c r="D49" t="s">
-        <v>126</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49" t="s">
-        <v>127</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="N49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" t="s">
-        <v>118</v>
-      </c>
-      <c r="C50">
-        <v>0.9990313649177551</v>
-      </c>
-      <c r="D50" t="s">
-        <v>126</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50" t="s">
-        <v>127</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
-      <c r="N50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" t="s">
-        <v>63</v>
-      </c>
-      <c r="B51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C51">
-        <v>0.9985432624816895</v>
-      </c>
-      <c r="D51" t="s">
-        <v>126</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51" t="s">
-        <v>127</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
-      <c r="N51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52" t="s">
-        <v>64</v>
-      </c>
-      <c r="B52" t="s">
-        <v>120</v>
-      </c>
-      <c r="C52">
-        <v>0.9841215014457703</v>
-      </c>
-      <c r="D52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52" t="s">
-        <v>127</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>1</v>
-      </c>
-      <c r="N52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" t="s">
-        <v>121</v>
-      </c>
-      <c r="C53">
-        <v>0.9983500838279724</v>
-      </c>
-      <c r="D53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53" t="b">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53" t="s">
-        <v>127</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>1</v>
-      </c>
-      <c r="N53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54" t="s">
-        <v>122</v>
-      </c>
-      <c r="C54">
-        <v>0.9809226989746094</v>
-      </c>
-      <c r="D54" t="s">
-        <v>126</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54" t="s">
-        <v>127</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>1</v>
-      </c>
-      <c r="N54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" t="s">
-        <v>67</v>
-      </c>
-      <c r="B55" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55">
-        <v>0.9973804354667664</v>
-      </c>
-      <c r="D55" t="s">
-        <v>126</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55" t="s">
-        <v>127</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>1</v>
-      </c>
-      <c r="N55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="A56" t="s">
-        <v>68</v>
-      </c>
-      <c r="B56" t="s">
-        <v>124</v>
-      </c>
-      <c r="C56">
-        <v>0.9980894923210144</v>
-      </c>
-      <c r="D56" t="s">
-        <v>126</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56" t="s">
-        <v>127</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>1</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" t="s">
-        <v>125</v>
-      </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3222,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -3238,6 +3580,12 @@
       </c>
       <c r="N57">
         <v>1</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/template/t6_ocr_report.xlsx
+++ b/template/t6_ocr_report.xlsx
@@ -64,55 +64,55 @@
     <t>is_double</t>
   </si>
   <si>
-    <t>micro_0074_YSA.jpg</t>
-  </si>
-  <si>
-    <t>micro_0055_XIV.jpg</t>
-  </si>
-  <si>
-    <t>micro_0000_XZI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0045_XZT.jpg</t>
-  </si>
-  <si>
-    <t>micro_0102_XN_K1224.jpg</t>
-  </si>
-  <si>
-    <t>micro_0027_XL_II.jpg</t>
-  </si>
-  <si>
-    <t>micro_0092_XL_I_HO_00.jpg</t>
-  </si>
-  <si>
-    <t>micro_0005_X8.jpg</t>
-  </si>
-  <si>
-    <t>micro_0056_X6.jpg</t>
-  </si>
-  <si>
-    <t>micro_0053_X5.jpg</t>
-  </si>
-  <si>
-    <t>micro_0054_X3.jpg</t>
-  </si>
-  <si>
-    <t>micro_0035_X_O_2460_0O0.jpg</t>
-  </si>
-  <si>
-    <t>micro_0085_HSIV.jpg</t>
-  </si>
-  <si>
-    <t>micro_0019_HSII.jpg</t>
-  </si>
-  <si>
-    <t>micro_0050_SI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0064_DOQOOSN.jpg</t>
-  </si>
-  <si>
-    <t>micro_0021_SA.jpg</t>
+    <t>micro_0120_YSA.jpg</t>
+  </si>
+  <si>
+    <t>micro_0118_XIV.jpg</t>
+  </si>
+  <si>
+    <t>micro_0003_XZI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0055_XZ.jpg</t>
+  </si>
+  <si>
+    <t>micro_0046_XNK1224_977.jpg</t>
+  </si>
+  <si>
+    <t>micro_0035_XL_II.jpg</t>
+  </si>
+  <si>
+    <t>micro_0111_XL_I.jpg</t>
+  </si>
+  <si>
+    <t>micro_0008_X8.jpg</t>
+  </si>
+  <si>
+    <t>micro_0066_X6.jpg</t>
+  </si>
+  <si>
+    <t>micro_0063_X5.jpg</t>
+  </si>
+  <si>
+    <t>micro_0064_X3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0093_XT.jpg</t>
+  </si>
+  <si>
+    <t>micro_0023_HSIV.jpg</t>
+  </si>
+  <si>
+    <t>micro_0024_SII.jpg</t>
+  </si>
+  <si>
+    <t>micro_0060_SI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0075_DOQOOSN.jpg</t>
+  </si>
+  <si>
+    <t>micro_0031_SA.jpg</t>
   </si>
   <si>
     <t>micro_0082_S8.jpg</t>
@@ -121,115 +121,115 @@
     <t>micro_0081_S6.jpg</t>
   </si>
   <si>
-    <t>micro_0071_S5.jpg</t>
-  </si>
-  <si>
-    <t>micro_0016_S3.jpg</t>
+    <t>micro_0083_S5.jpg</t>
+  </si>
+  <si>
+    <t>micro_0021_S3.jpg</t>
   </si>
   <si>
     <t>micro_0001_0OQOO_S.jpg</t>
   </si>
   <si>
-    <t>micro_0067_D9.jpg</t>
-  </si>
-  <si>
-    <t>micro_0039_D7.jpg</t>
-  </si>
-  <si>
-    <t>micro_0063_D6.jpg</t>
-  </si>
-  <si>
-    <t>micro_0091_D58.jpg</t>
-  </si>
-  <si>
-    <t>micro_0060_D56.jpg</t>
-  </si>
-  <si>
-    <t>micro_0094_D52.jpg</t>
-  </si>
-  <si>
-    <t>micro_0003_D50.jpg</t>
-  </si>
-  <si>
-    <t>micro_0041_D5.jpg</t>
-  </si>
-  <si>
-    <t>micro_0024_D48.jpg</t>
-  </si>
-  <si>
-    <t>micro_0026_D46_K1226_344.jpg</t>
-  </si>
-  <si>
-    <t>micro_0025_D44.jpg</t>
-  </si>
-  <si>
-    <t>micro_0059_D40.jpg</t>
-  </si>
-  <si>
-    <t>micro_0023_D4.jpg</t>
-  </si>
-  <si>
-    <t>micro_0012_D38.jpg</t>
-  </si>
-  <si>
-    <t>micro_0058_D36.jpg</t>
-  </si>
-  <si>
-    <t>micro_0048_D34.jpg</t>
-  </si>
-  <si>
-    <t>micro_0013_D32.jpg</t>
-  </si>
-  <si>
-    <t>micro_0008_D30.jpg</t>
-  </si>
-  <si>
-    <t>micro_0037_D3.jpg</t>
-  </si>
-  <si>
-    <t>micro_0046_D28.jpg</t>
-  </si>
-  <si>
-    <t>micro_0078_D26.jpg</t>
-  </si>
-  <si>
-    <t>micro_0032_D24.jpg</t>
-  </si>
-  <si>
-    <t>micro_0031_D22.jpg</t>
-  </si>
-  <si>
-    <t>micro_0010_D20.jpg</t>
-  </si>
-  <si>
-    <t>micro_0022_D2.jpg</t>
-  </si>
-  <si>
-    <t>micro_0011_D18.jpg</t>
-  </si>
-  <si>
-    <t>micro_0086_D17.jpg</t>
-  </si>
-  <si>
-    <t>micro_0077_0D16.jpg</t>
-  </si>
-  <si>
-    <t>micro_0087_D15.jpg</t>
-  </si>
-  <si>
-    <t>micro_0052_D14.jpg</t>
-  </si>
-  <si>
-    <t>micro_0044_D13.jpg</t>
-  </si>
-  <si>
-    <t>micro_0076_D12.jpg</t>
-  </si>
-  <si>
-    <t>micro_0042_D11.jpg</t>
-  </si>
-  <si>
-    <t>micro_0036_D1.jpg</t>
+    <t>micro_0052_D9.jpg</t>
+  </si>
+  <si>
+    <t>micro_0048_D7.jpg</t>
+  </si>
+  <si>
+    <t>micro_0074_D6.jpg</t>
+  </si>
+  <si>
+    <t>micro_0107_D58.jpg</t>
+  </si>
+  <si>
+    <t>micro_0071_D56.jpg</t>
+  </si>
+  <si>
+    <t>micro_0110_D52.jpg</t>
+  </si>
+  <si>
+    <t>micro_0109_D50.jpg</t>
+  </si>
+  <si>
+    <t>micro_0050_D5.jpg</t>
+  </si>
+  <si>
+    <t>micro_0005_D48.jpg</t>
+  </si>
+  <si>
+    <t>micro_0034_D46_K1226_344.jpg</t>
+  </si>
+  <si>
+    <t>micro_0033_D44.jpg</t>
+  </si>
+  <si>
+    <t>micro_0070_D40.jpg</t>
+  </si>
+  <si>
+    <t>micro_0030_D4.jpg</t>
+  </si>
+  <si>
+    <t>micro_0017_D38.jpg</t>
+  </si>
+  <si>
+    <t>micro_0069_D36.jpg</t>
+  </si>
+  <si>
+    <t>micro_0019_D34.jpg</t>
+  </si>
+  <si>
+    <t>micro_0018_D32.jpg</t>
+  </si>
+  <si>
+    <t>micro_0013_D30.jpg</t>
+  </si>
+  <si>
+    <t>micro_0045_D3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0056_D28.jpg</t>
+  </si>
+  <si>
+    <t>micro_0011_D26.jpg</t>
+  </si>
+  <si>
+    <t>micro_0040_D24.jpg</t>
+  </si>
+  <si>
+    <t>micro_0039_D22.jpg</t>
+  </si>
+  <si>
+    <t>micro_0015_D20.jpg</t>
+  </si>
+  <si>
+    <t>micro_0029_D2.jpg</t>
+  </si>
+  <si>
+    <t>micro_0088_D18.jpg</t>
+  </si>
+  <si>
+    <t>micro_0101_D17.jpg</t>
+  </si>
+  <si>
+    <t>micro_0091_D16.jpg</t>
+  </si>
+  <si>
+    <t>micro_0102_D15.jpg</t>
+  </si>
+  <si>
+    <t>micro_0113_D14.jpg</t>
+  </si>
+  <si>
+    <t>micro_0014_D13.jpg</t>
+  </si>
+  <si>
+    <t>micro_0089_D12.jpg</t>
+  </si>
+  <si>
+    <t>micro_0051_D11.jpg</t>
+  </si>
+  <si>
+    <t>micro_0044_D1.jpg</t>
   </si>
   <si>
     <t>YSA</t>
@@ -796,7 +796,7 @@
         <v>72</v>
       </c>
       <c r="C2">
-        <v>0.9988731741905212</v>
+        <v>0.9988832473754883</v>
       </c>
       <c r="D2" t="s">
         <v>128</v>
@@ -829,7 +829,7 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>73</v>
       </c>
       <c r="C3">
-        <v>0.9954721331596375</v>
+        <v>0.9839360117912292</v>
       </c>
       <c r="D3" t="s">
         <v>128</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -896,7 +896,7 @@
         <v>74</v>
       </c>
       <c r="C4">
-        <v>0.9048922061920166</v>
+        <v>0.9625399708747864</v>
       </c>
       <c r="D4" t="s">
         <v>128</v>
@@ -946,7 +946,7 @@
         <v>75</v>
       </c>
       <c r="C5">
-        <v>0.8647018074989319</v>
+        <v>0.994958758354187</v>
       </c>
       <c r="D5" t="s">
         <v>128</v>
@@ -996,7 +996,7 @@
         <v>76</v>
       </c>
       <c r="C6">
-        <v>0.9972390532493591</v>
+        <v>0.9973981976509094</v>
       </c>
       <c r="D6" t="s">
         <v>128</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1096,7 +1096,7 @@
         <v>78</v>
       </c>
       <c r="C8">
-        <v>0.9225170612335205</v>
+        <v>0.921156108379364</v>
       </c>
       <c r="D8" t="s">
         <v>128</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1396,7 +1396,7 @@
         <v>84</v>
       </c>
       <c r="C14">
-        <v>0.99773770570755</v>
+        <v>0.9987279772758484</v>
       </c>
       <c r="D14" t="s">
         <v>128</v>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>85</v>
       </c>
       <c r="C15">
-        <v>0.8552407622337341</v>
+        <v>0.9159612655639648</v>
       </c>
       <c r="D15" t="s">
         <v>128</v>
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>88</v>
       </c>
       <c r="C18">
-        <v>0.9971151351928711</v>
+        <v>0.997856616973877</v>
       </c>
       <c r="D18" t="s">
         <v>128</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1646,7 +1646,7 @@
         <v>89</v>
       </c>
       <c r="C19">
-        <v>0.9920763969421387</v>
+        <v>0.9957458972930908</v>
       </c>
       <c r="D19" t="s">
         <v>128</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>90</v>
       </c>
       <c r="C20">
-        <v>0.9916169047355652</v>
+        <v>0.996196985244751</v>
       </c>
       <c r="D20" t="s">
         <v>128</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>94</v>
       </c>
       <c r="C24">
-        <v>0.9977332353591919</v>
+        <v>0.9961812496185303</v>
       </c>
       <c r="D24" t="s">
         <v>128</v>
@@ -1929,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>0.9767656326293945</v>
+        <v>0.9834635853767395</v>
       </c>
       <c r="D30" t="s">
         <v>128</v>
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>102</v>
       </c>
       <c r="C32">
-        <v>0.9783324599266052</v>
+        <v>0.9841743111610413</v>
       </c>
       <c r="D32" t="s">
         <v>128</v>
@@ -2329,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>1</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -2479,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="N36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -2579,7 +2579,7 @@
         <v>1</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -2629,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>109</v>
       </c>
       <c r="C39">
-        <v>0.9964321255683899</v>
+        <v>0.9993095397949219</v>
       </c>
       <c r="D39" t="s">
         <v>128</v>
@@ -2679,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="N40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>111</v>
       </c>
       <c r="C41">
-        <v>0.9894289374351501</v>
+        <v>0.9846103191375732</v>
       </c>
       <c r="D41" t="s">
         <v>128</v>
@@ -2779,7 +2779,7 @@
         <v>1</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="N42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>114</v>
       </c>
       <c r="C44">
-        <v>0.9977620244026184</v>
+        <v>0.9981024861335754</v>
       </c>
       <c r="D44" t="s">
         <v>128</v>
@@ -2929,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -3129,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>119</v>
       </c>
       <c r="C49">
-        <v>0.9984526634216309</v>
+        <v>0.9995148777961731</v>
       </c>
       <c r="D49" t="s">
         <v>128</v>
@@ -3179,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -3229,7 +3229,7 @@
         <v>1</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>121</v>
       </c>
       <c r="C51">
-        <v>0.9987942576408386</v>
+        <v>0.9987363219261169</v>
       </c>
       <c r="D51" t="s">
         <v>128</v>
@@ -3279,7 +3279,7 @@
         <v>1</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>123</v>
       </c>
       <c r="C53">
-        <v>0.9983298182487488</v>
+        <v>0.9979743361473083</v>
       </c>
       <c r="D53" t="s">
         <v>128</v>
@@ -3379,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>124</v>
       </c>
       <c r="C54">
-        <v>0.9798585176467896</v>
+        <v>0.8948138952255249</v>
       </c>
       <c r="D54" t="s">
         <v>128</v>
@@ -3429,7 +3429,7 @@
         <v>1</v>
       </c>
       <c r="N54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -3529,7 +3529,7 @@
         <v>1</v>
       </c>
       <c r="N56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -3579,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57">
         <v>0</v>
